--- a/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/ACO/resultados_parametros_pop_1.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/ACO/resultados_parametros_pop_1.xlsx
@@ -448,7 +448,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.996506</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>0.2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.98521</v>
+        <v>0.9963070000000001</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>0.3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9963070000000001</v>
       </c>
     </row>
     <row r="5">
@@ -472,7 +472,7 @@
         <v>0.4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.985112</v>
+        <v>0.996606</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
         <v>0.5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.996705</v>
       </c>
     </row>
     <row r="7"/>

--- a/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/ACO/resultados_parametros_pop_1.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/ACO/resultados_parametros_pop_1.xlsx
@@ -428,13 +428,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Taxa de Evaporação</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -448,42 +448,66 @@
         <v>0.1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.996506</v>
+        <v>0.994684</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.9963070000000001</v>
+        <v>0.991227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9963070000000001</v>
+        <v>0.993101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.996606</v>
+        <v>0.993289</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.996705</v>
-      </c>
-    </row>
-    <row r="7"/>
+        <v>0.994684</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.993306</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.992995</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.993205</v>
+      </c>
+    </row>
+    <row r="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
